--- a/design/templates/generated/Northwestern/CATTLE_FLOOD_NWE_V1_upload_template.xlsx
+++ b/design/templates/generated/Northwestern/CATTLE_FLOOD_NWE_V1_upload_template.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2020-2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-2030" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2021-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-2030" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEIGHTS" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_META" sheetId="5" state="hidden" r:id="rId5"/>
@@ -566,7 +566,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAW DATA 2020-2025 - Livestock Sector / Cattle Farming - Flood - Northwestern Province   [profile CATTLE_FLOOD_NWE_V1]   |   Enter RAW values only - the system normalizes.</t>
+          <t>RAW DATA 2021-2025 - Livestock Sector / Cattle Farming - Flood - Northwestern Province   [profile CATTLE_FLOOD_NWE_V1]   |   Enter RAW values only - the system normalizes.</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2025</v>
@@ -934,7 +934,7 @@
       </c>
       <c r="Y4" s="6" t="inlineStr">
         <is>
-          <t>Dept. report 2020-2025</t>
+          <t>Dept. report 2021-2025</t>
         </is>
       </c>
       <c r="Z4" s="6" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>NWE-001</t>
+          <t>KU1</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>2025</v>
@@ -990,7 +990,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>NWE-002</t>
+          <t>KU2</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>2025</v>
@@ -1034,7 +1034,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>NWE-003</t>
+          <t>KU3</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>2025</v>
@@ -1078,7 +1078,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>NWE-004</t>
+          <t>KU4</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>2025</v>
@@ -1122,7 +1122,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>NWE-005</t>
+          <t>KU5</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>2025</v>
@@ -1166,7 +1166,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>NWE-006</t>
+          <t>KU6</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>2025</v>
@@ -1210,7 +1210,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>NWE-007</t>
+          <t>KU7</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>2025</v>
@@ -1254,7 +1254,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>NWE-008</t>
+          <t>KU8</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>2025</v>
@@ -1298,7 +1298,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>NWE-009</t>
+          <t>KU9</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>2025</v>
@@ -1342,7 +1342,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>NWE-010</t>
+          <t>KU10</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>2025</v>
@@ -1386,7 +1386,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>NWE-011</t>
+          <t>KU11</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>2025</v>
@@ -1430,7 +1430,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>NWE-012</t>
+          <t>KU12</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2025</v>
@@ -1474,7 +1474,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>NWE-013</t>
+          <t>KU13</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>2025</v>
@@ -1518,7 +1518,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>NWE-014</t>
+          <t>KU14</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>2025</v>
@@ -1562,7 +1562,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>NWE-015</t>
+          <t>KU15</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>2025</v>
@@ -1606,7 +1606,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>NWE-016</t>
+          <t>KU16</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>2025</v>
@@ -1650,7 +1650,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>NWE-017</t>
+          <t>KU17</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>2025</v>
@@ -1694,7 +1694,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>NWE-018</t>
+          <t>KU18</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>2025</v>
@@ -1738,7 +1738,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>NWE-019</t>
+          <t>KU19</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>2025</v>
@@ -1782,7 +1782,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>NWE-020</t>
+          <t>KU20</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>2025</v>
@@ -1826,7 +1826,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>NWE-021</t>
+          <t>KU21</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>2025</v>
@@ -1870,7 +1870,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>NWE-022</t>
+          <t>KU22</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>2025</v>
@@ -1914,7 +1914,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>NWE-023</t>
+          <t>KU23</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>2025</v>
@@ -1958,7 +1958,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>NWE-024</t>
+          <t>KU24</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>2025</v>
@@ -2002,7 +2002,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>NWE-025</t>
+          <t>KU25</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>2025</v>
@@ -2046,7 +2046,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>NWE-026</t>
+          <t>KU26</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>2025</v>
@@ -2090,7 +2090,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>NWE-027</t>
+          <t>KU27</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>2025</v>
@@ -2134,7 +2134,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>NWE-028</t>
+          <t>KU28</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>2025</v>
@@ -2178,7 +2178,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>NWE-029</t>
+          <t>KU29</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>2025</v>
@@ -2222,7 +2222,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>NWE-030</t>
+          <t>KU30</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>2025</v>
@@ -2266,7 +2266,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>NWE-031</t>
+          <t>PU1</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>2025</v>
@@ -2310,7 +2310,7 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>NWE-032</t>
+          <t>PU2</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>2025</v>
@@ -2354,7 +2354,7 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>NWE-033</t>
+          <t>PU3</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>2025</v>
@@ -2398,7 +2398,7 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>NWE-034</t>
+          <t>PU4</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>2025</v>
@@ -2442,7 +2442,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>NWE-035</t>
+          <t>PU5</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>2025</v>
@@ -2486,7 +2486,7 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>NWE-036</t>
+          <t>PU6</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>2025</v>
@@ -2530,7 +2530,7 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>NWE-037</t>
+          <t>PU7</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>2025</v>
@@ -2574,7 +2574,7 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>NWE-038</t>
+          <t>PU8</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -2588,7 +2588,7 @@
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>2025</v>
@@ -2618,7 +2618,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>NWE-039</t>
+          <t>PU9</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>2025</v>
@@ -2662,7 +2662,7 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>NWE-040</t>
+          <t>PU10</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>2025</v>
@@ -2706,7 +2706,7 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>NWE-041</t>
+          <t>PU11</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E45" s="7" t="n">
         <v>2025</v>
@@ -2750,7 +2750,7 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>NWE-042</t>
+          <t>PU12</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E46" s="7" t="n">
         <v>2025</v>
@@ -2794,7 +2794,7 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>NWE-043</t>
+          <t>PU13</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E47" s="7" t="n">
         <v>2025</v>
@@ -2838,7 +2838,7 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>NWE-044</t>
+          <t>PU14</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E48" s="7" t="n">
         <v>2025</v>
@@ -2882,7 +2882,7 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>NWE-045</t>
+          <t>PU15</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E49" s="7" t="n">
         <v>2025</v>
@@ -2926,7 +2926,7 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>NWE-046</t>
+          <t>PU16</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E50" s="7" t="n">
         <v>2025</v>
@@ -2968,7 +2968,6 @@
       <c r="Z50" s="8" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Z1"/>
   </mergeCells>
@@ -3021,7 +3020,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAW DATA 2025-2030 - Livestock Sector / Cattle Farming - Flood - Northwestern Province   [profile CATTLE_FLOOD_NWE_V1]   |   Enter RAW values only - the system normalizes.</t>
+          <t>RAW DATA 2026-2030 - Livestock Sector / Cattle Farming - Flood - Northwestern Province   [profile CATTLE_FLOOD_NWE_V1]   |   Enter RAW values only - the system normalizes.</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3324,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2030</v>
@@ -3389,7 +3388,7 @@
       </c>
       <c r="Y4" s="6" t="inlineStr">
         <is>
-          <t>Dept. report 2025-2030</t>
+          <t>Dept. report 2026-2030</t>
         </is>
       </c>
       <c r="Z4" s="6" t="inlineStr">
@@ -3401,7 +3400,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>NWE-001</t>
+          <t>KU1</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -3415,7 +3414,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>2030</v>
@@ -3445,7 +3444,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>NWE-002</t>
+          <t>KU2</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -3459,7 +3458,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>2030</v>
@@ -3489,7 +3488,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>NWE-003</t>
+          <t>KU3</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -3503,7 +3502,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>2030</v>
@@ -3533,7 +3532,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>NWE-004</t>
+          <t>KU4</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -3547,7 +3546,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>2030</v>
@@ -3577,7 +3576,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>NWE-005</t>
+          <t>KU5</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -3591,7 +3590,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>2030</v>
@@ -3621,7 +3620,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>NWE-006</t>
+          <t>KU6</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -3635,7 +3634,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>2030</v>
@@ -3665,7 +3664,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>NWE-007</t>
+          <t>KU7</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -3679,7 +3678,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>2030</v>
@@ -3709,7 +3708,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>NWE-008</t>
+          <t>KU8</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -3723,7 +3722,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>2030</v>
@@ -3753,7 +3752,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>NWE-009</t>
+          <t>KU9</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -3767,7 +3766,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>2030</v>
@@ -3797,7 +3796,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>NWE-010</t>
+          <t>KU10</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -3811,7 +3810,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>2030</v>
@@ -3841,7 +3840,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>NWE-011</t>
+          <t>KU11</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -3855,7 +3854,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>2030</v>
@@ -3885,7 +3884,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>NWE-012</t>
+          <t>KU12</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -3899,7 +3898,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2030</v>
@@ -3929,7 +3928,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>NWE-013</t>
+          <t>KU13</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -3943,7 +3942,7 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>2030</v>
@@ -3973,7 +3972,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>NWE-014</t>
+          <t>KU14</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -3987,7 +3986,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>2030</v>
@@ -4017,7 +4016,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>NWE-015</t>
+          <t>KU15</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -4031,7 +4030,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>2030</v>
@@ -4061,7 +4060,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>NWE-016</t>
+          <t>KU16</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -4075,7 +4074,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>2030</v>
@@ -4105,7 +4104,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>NWE-017</t>
+          <t>KU17</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -4119,7 +4118,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>2030</v>
@@ -4149,7 +4148,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>NWE-018</t>
+          <t>KU18</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -4163,7 +4162,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>2030</v>
@@ -4193,7 +4192,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>NWE-019</t>
+          <t>KU19</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -4207,7 +4206,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>2030</v>
@@ -4237,7 +4236,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>NWE-020</t>
+          <t>KU20</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -4251,7 +4250,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>2030</v>
@@ -4281,7 +4280,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>NWE-021</t>
+          <t>KU21</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -4295,7 +4294,7 @@
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>2030</v>
@@ -4325,7 +4324,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>NWE-022</t>
+          <t>KU22</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -4339,7 +4338,7 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>2030</v>
@@ -4369,7 +4368,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>NWE-023</t>
+          <t>KU23</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -4383,7 +4382,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>2030</v>
@@ -4413,7 +4412,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>NWE-024</t>
+          <t>KU24</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -4427,7 +4426,7 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>2030</v>
@@ -4457,7 +4456,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>NWE-025</t>
+          <t>KU25</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -4471,7 +4470,7 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>2030</v>
@@ -4501,7 +4500,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>NWE-026</t>
+          <t>KU26</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -4515,7 +4514,7 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>2030</v>
@@ -4545,7 +4544,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>NWE-027</t>
+          <t>KU27</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -4559,7 +4558,7 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>2030</v>
@@ -4589,7 +4588,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>NWE-028</t>
+          <t>KU28</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -4603,7 +4602,7 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>2030</v>
@@ -4633,7 +4632,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>NWE-029</t>
+          <t>KU29</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -4647,7 +4646,7 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>2030</v>
@@ -4677,7 +4676,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>NWE-030</t>
+          <t>KU30</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -4691,7 +4690,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>2030</v>
@@ -4721,7 +4720,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>NWE-031</t>
+          <t>PU1</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -4735,7 +4734,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>2030</v>
@@ -4765,7 +4764,7 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>NWE-032</t>
+          <t>PU2</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -4779,7 +4778,7 @@
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>2030</v>
@@ -4809,7 +4808,7 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>NWE-033</t>
+          <t>PU3</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -4823,7 +4822,7 @@
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>2030</v>
@@ -4853,7 +4852,7 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>NWE-034</t>
+          <t>PU4</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -4867,7 +4866,7 @@
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>2030</v>
@@ -4897,7 +4896,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>NWE-035</t>
+          <t>PU5</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -4911,7 +4910,7 @@
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>2030</v>
@@ -4941,7 +4940,7 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>NWE-036</t>
+          <t>PU6</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -4955,7 +4954,7 @@
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>2030</v>
@@ -4985,7 +4984,7 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>NWE-037</t>
+          <t>PU7</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -4999,7 +4998,7 @@
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>2030</v>
@@ -5029,7 +5028,7 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>NWE-038</t>
+          <t>PU8</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -5043,7 +5042,7 @@
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>2030</v>
@@ -5073,7 +5072,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>NWE-039</t>
+          <t>PU9</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -5087,7 +5086,7 @@
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>2030</v>
@@ -5117,7 +5116,7 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>NWE-040</t>
+          <t>PU10</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -5131,7 +5130,7 @@
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>2030</v>
@@ -5161,7 +5160,7 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>NWE-041</t>
+          <t>PU11</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -5175,7 +5174,7 @@
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E45" s="7" t="n">
         <v>2030</v>
@@ -5205,7 +5204,7 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>NWE-042</t>
+          <t>PU12</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -5219,7 +5218,7 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E46" s="7" t="n">
         <v>2030</v>
@@ -5249,7 +5248,7 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>NWE-043</t>
+          <t>PU13</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -5263,7 +5262,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E47" s="7" t="n">
         <v>2030</v>
@@ -5293,7 +5292,7 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>NWE-044</t>
+          <t>PU14</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -5307,7 +5306,7 @@
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E48" s="7" t="n">
         <v>2030</v>
@@ -5337,7 +5336,7 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>NWE-045</t>
+          <t>PU15</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -5351,7 +5350,7 @@
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E49" s="7" t="n">
         <v>2030</v>
@@ -5381,7 +5380,7 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>NWE-046</t>
+          <t>PU16</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -5395,7 +5394,7 @@
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E50" s="7" t="n">
         <v>2030</v>
@@ -5423,7 +5422,6 @@
       <c r="Z50" s="8" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Z1"/>
   </mergeCells>
@@ -5442,7 +5440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5451,6 +5449,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5498,6 +5497,11 @@
           <t>PROPOSED WEIGHT % (read at import)</t>
         </is>
       </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>basis of the proposal</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -5518,6 +5522,7 @@
       <c r="D4" s="11" t="n"/>
       <c r="E4" s="11" t="n"/>
       <c r="F4" s="12" t="n"/>
+      <c r="G4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -5546,6 +5551,7 @@
       <c r="F5" s="12" t="n">
         <v>100</v>
       </c>
+      <c r="G5" s="13" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -5566,6 +5572,7 @@
       <c r="D6" s="11" t="n"/>
       <c r="E6" s="11" t="n"/>
       <c r="F6" s="12" t="n"/>
+      <c r="G6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -5586,6 +5593,7 @@
       <c r="D7" s="11" t="n"/>
       <c r="E7" s="11" t="n"/>
       <c r="F7" s="12" t="n"/>
+      <c r="G7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -5606,6 +5614,7 @@
       <c r="D8" s="11" t="n"/>
       <c r="E8" s="11" t="n"/>
       <c r="F8" s="12" t="n"/>
+      <c r="G8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
@@ -5626,6 +5635,7 @@
       <c r="D9" s="11" t="n"/>
       <c r="E9" s="11" t="n"/>
       <c r="F9" s="12" t="n"/>
+      <c r="G9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -5654,6 +5664,7 @@
       <c r="F10" s="12" t="n">
         <v>15</v>
       </c>
+      <c r="G10" s="13" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -5682,6 +5693,7 @@
       <c r="F11" s="12" t="n">
         <v>10</v>
       </c>
+      <c r="G11" s="13" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -5710,6 +5722,7 @@
       <c r="F12" s="12" t="n">
         <v>10</v>
       </c>
+      <c r="G12" s="13" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -5730,6 +5743,7 @@
       <c r="D13" s="11" t="n"/>
       <c r="E13" s="11" t="n"/>
       <c r="F13" s="12" t="n"/>
+      <c r="G13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -5750,6 +5764,7 @@
       <c r="D14" s="11" t="n"/>
       <c r="E14" s="11" t="n"/>
       <c r="F14" s="12" t="n"/>
+      <c r="G14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
@@ -5778,6 +5793,7 @@
       <c r="F15" s="12" t="n">
         <v>15</v>
       </c>
+      <c r="G15" s="13" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -5798,6 +5814,7 @@
       <c r="D16" s="11" t="n"/>
       <c r="E16" s="11" t="n"/>
       <c r="F16" s="12" t="n"/>
+      <c r="G16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
@@ -5826,6 +5843,7 @@
       <c r="F17" s="12" t="n">
         <v>5</v>
       </c>
+      <c r="G17" s="13" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
@@ -5846,6 +5864,7 @@
       <c r="D18" s="11" t="n"/>
       <c r="E18" s="11" t="n"/>
       <c r="F18" s="12" t="n"/>
+      <c r="G18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
@@ -5874,6 +5893,7 @@
       <c r="F19" s="12" t="n">
         <v>15</v>
       </c>
+      <c r="G19" s="13" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
@@ -5902,6 +5922,7 @@
       <c r="F20" s="12" t="n">
         <v>5</v>
       </c>
+      <c r="G20" s="13" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -5922,6 +5943,7 @@
       <c r="D21" s="11" t="n"/>
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="12" t="n"/>
+      <c r="G21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
@@ -5950,6 +5972,7 @@
       <c r="F22" s="12" t="n">
         <v>10</v>
       </c>
+      <c r="G22" s="13" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
@@ -5974,9 +5997,8 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid weight" error="Weight must be between 0 and 100." type="decimal" operator="between">
@@ -6015,14 +6037,14 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Profile: CATTLE_FLOOD_NWE_V1   |   generated 2026-07-29 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
+          <t>Profile: CATTLE_FLOOD_NWE_V1   |   generated 2026-09-03 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>1. One tab per data period (2020-2025, 2025-2030). Fill the tab matching your dataset's period; skip tabs with no data.</t>
+          <t>1. One tab per data period (2021-2025, 2026-2030). Fill the tab matching your dataset's period; skip tabs with no data.</t>
         </is>
       </c>
     </row>
@@ -6036,14 +6058,14 @@
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>2b. The year 2025 appears in both tabs. If a year sits in two periods the system uses the LATER period's value, so nothing is counted twice.</t>
+          <t>2b. The two periods are contiguous and do not overlap (changed 2026-09-03 at the Central panel's request - the old 2020-2025 / 2025-2030 pair shared the year 2025 and needed a tie-break). Every year belongs to exactly one tab.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>3. Edit ONLY the yellow cells. Division codes, names, district and the period columns are pre-filled and locked.</t>
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>3. REVIEW COPY - nothing is locked. The yellow cells are still where data belongs, but every cell, header and tab can be changed so the panel can mark up structure as well as values. Return the marked-up file; the finalised version will be re-issued locked for collection.</t>
         </is>
       </c>
     </row>
@@ -6057,7 +6079,7 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>5. Do not add, remove, rename or reorder columns or tabs. Files with changed structure are rejected on import.</t>
+          <t>5. Structural changes ARE invited in this review copy - add, rename or reorder columns and note what you changed. This file is NOT importable; the locked re-issue is.</t>
         </is>
       </c>
     </row>
@@ -6649,7 +6671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6737,80 +6759,104 @@
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>generated</t>
+          <t>protection</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>unlocked-review</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>dsd_level</t>
+          <t>panel_overrides</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>DS_DIVISION</t>
+          <t>0 add, 0 retire</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>periods</t>
+          <t>generated</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>2020-2025|2025-2030</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>n_variables</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="n">
-        <v>19</v>
+          <t>dsd_level</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>DS_DIVISION</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>period_rule_default</t>
+          <t>periods</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>average (typical year); 2025 -&gt; latest period wins</t>
+          <t>2021-2025|2026-2030</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>period_aggregation</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>FLOOD_EVENTS_1974_TO_2023=fixed_window|FLOOD_HAZARD_INDEX=fixed_window|LIGHTNING_INCIDENTS_1974_TO_2023=fixed_window|STRONG_WIND_EVENTS_1978_TO_2023=fixed_window|VERY_WET_DAYS=average|CATTLE_FARMERS=average|CATTLE_FARMS=average|CATTLE_MILK_PRODUCTION_FARMS=average|CATTLE_POPULATION=average|LIVESTOCK_FARMERS=average|MITCH_COWS_ANNUAL_MILK_PRODUCTION=average|MITCH_COWS_DAILY_MILK_PRODUCTION=average|MITCH_COWS_MONTHLY_MILK_PRODUCTION=average|PASTURE_FODDER_EXTENT_ACRE=average|PCT_CATTLE_FARMERS_LIVESTOCK_OPERATORS=average|PCT_EXTENSIVE=average|PCT_INTENSIVE=average|PCT_LIVESTOCK_FARMERS_AGRICULTURAL_OPERATORS=average|PCT_SEMI_INTENSIVE=average</t>
-        </is>
+          <t>n_variables</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
+          <t>period_rule_default</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>average (typical year); periods are contiguous, no overlap</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>period_aggregation</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>FLOOD_EVENTS_1974_TO_2023=fixed_window|FLOOD_HAZARD_INDEX=fixed_window|LIGHTNING_INCIDENTS_1974_TO_2023=fixed_window|STRONG_WIND_EVENTS_1978_TO_2023=fixed_window|VERY_WET_DAYS=average|CATTLE_FARMERS=average|CATTLE_FARMS=average|CATTLE_MILK_PRODUCTION_FARMS=average|CATTLE_POPULATION=average|LIVESTOCK_FARMERS=average|MITCH_COWS_ANNUAL_MILK_PRODUCTION=average|MITCH_COWS_DAILY_MILK_PRODUCTION=average|MITCH_COWS_MONTHLY_MILK_PRODUCTION=average|PASTURE_FODDER_EXTENT_ACRE=average|PCT_CATTLE_FARMERS_LIVESTOCK_OPERATORS=average|PCT_EXTENSIVE=average|PCT_INTENSIVE=average|PCT_LIVESTOCK_FARMERS_AGRICULTURAL_OPERATORS=average|PCT_SEMI_INTENSIVE=average</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
           <t>expected_columns</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>DS_CODE|DS_DIVISION|DISTRICT|YEAR_START|YEAR_END|FLOOD_EVENTS_1974_TO_2023|FLOOD_HAZARD_INDEX|LIGHTNING_INCIDENTS_1974_TO_2023|STRONG_WIND_EVENTS_1978_TO_2023|VERY_WET_DAYS|CATTLE_FARMERS|CATTLE_FARMS|CATTLE_MILK_PRODUCTION_FARMS|CATTLE_POPULATION|LIVESTOCK_FARMERS|MITCH_COWS_ANNUAL_MILK_PRODUCTION|MITCH_COWS_DAILY_MILK_PRODUCTION|MITCH_COWS_MONTHLY_MILK_PRODUCTION|PASTURE_FODDER_EXTENT_ACRE|PCT_CATTLE_FARMERS_LIVESTOCK_OPERATORS|PCT_EXTENSIVE|PCT_INTENSIVE|PCT_LIVESTOCK_FARMERS_AGRICULTURAL_OPERATORS|PCT_SEMI_INTENSIVE|DATA_SOURCE|NOTES</t>
         </is>

--- a/design/templates/generated/Northwestern/CATTLE_FLOOD_NWE_V1_upload_template.xlsx
+++ b/design/templates/generated/Northwestern/CATTLE_FLOOD_NWE_V1_upload_template.xlsx
@@ -6037,7 +6037,7 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Profile: CATTLE_FLOOD_NWE_V1   |   generated 2026-09-03 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
+          <t>Profile: CATTLE_FLOOD_NWE_V1   |   generated 2026-09-14 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
         </is>
       </c>
     </row>
@@ -6063,9 +6063,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>3. REVIEW COPY - nothing is locked. The yellow cells are still where data belongs, but every cell, header and tab can be changed so the panel can mark up structure as well as values. Return the marked-up file; the finalised version will be re-issued locked for collection.</t>
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>3. The yellow cells are where data belongs. Division codes, names, district and the period columns are pre-filled - change one only to correct a genuine error. Nothing in this file is protected, so please treat that as the instruction it is; the importer checks those columns and will refuse what it cannot match.</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>5. Structural changes ARE invited in this review copy - add, rename or reorder columns and note what you changed. This file is NOT importable; the locked re-issue is.</t>
+          <t>5. Do not add, remove, rename or reorder columns or tabs. Excel will now let you - the sheet is not protected - but the importer will not: the hidden _META tab states this file's column contract and a file whose structure has changed is refused, naming what changed. Nothing loads partially, so a rejected file loads nothing at all.</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>unlocked-review</t>
+          <t>locked</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
